--- a/TablaTASAS_3Graficos.xlsx
+++ b/TablaTASAS_3Graficos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Downloads\TABLERO_STREAMLIT_DASHBOARD\DASHBOARD_Morbilidad_DESPLIEGUE_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{235DC58B-B766-4DF6-A03F-8F208BE08B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F700BA38-C5AA-4339-9C3D-724324DC7C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="2" xr2:uid="{789166E0-528F-4FCB-ACD4-F09C6F4E7F42}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{789166E0-528F-4FCB-ACD4-F09C6F4E7F42}"/>
   </bookViews>
   <sheets>
     <sheet name="1_EdadCategori_TasaMorbi" sheetId="5" r:id="rId1"/>
@@ -500,7 +500,7 @@
         <v>7604.1227999998555</v>
       </c>
       <c r="D2" s="5">
-        <v>3.98</v>
+        <v>39.799999999999997</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -514,7 +514,7 @@
         <v>12711.643200000235</v>
       </c>
       <c r="D3" s="5">
-        <v>4.0599999999999996</v>
+        <v>40.599999999999994</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -528,7 +528,7 @@
         <v>16741.517700000284</v>
       </c>
       <c r="D4" s="5">
-        <v>3.11</v>
+        <v>31.099999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -542,7 +542,7 @@
         <v>92245.471600001867</v>
       </c>
       <c r="D5" s="5">
-        <v>1.25</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -556,7 +556,7 @@
         <v>45984.467599998556</v>
       </c>
       <c r="D6" s="5">
-        <v>1.97</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -570,7 +570,7 @@
         <v>6845.1031000000949</v>
       </c>
       <c r="D7" s="5">
-        <v>5.62</v>
+        <v>56.2</v>
       </c>
     </row>
   </sheetData>
@@ -608,7 +608,7 @@
         <v>15640.1</v>
       </c>
       <c r="D2" s="5">
-        <v>1.7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -622,7 +622,7 @@
         <v>11311.6</v>
       </c>
       <c r="D3" s="5">
-        <v>1.34</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -636,7 +636,7 @@
         <v>13832.7</v>
       </c>
       <c r="D4" s="5">
-        <v>1.64</v>
+        <v>16.399999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -650,7 +650,7 @@
         <v>17491.2</v>
       </c>
       <c r="D5" s="5">
-        <v>1.62</v>
+        <v>16.200000000000003</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -664,7 +664,7 @@
         <v>24981.3</v>
       </c>
       <c r="D6" s="5">
-        <v>2.37</v>
+        <v>23.700000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -678,7 +678,7 @@
         <v>21812.1</v>
       </c>
       <c r="D7" s="5">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -692,7 +692,7 @@
         <v>24940.6</v>
       </c>
       <c r="D8" s="5">
-        <v>2.21</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -706,7 +706,7 @@
         <v>24984.2</v>
       </c>
       <c r="D9" s="5">
-        <v>2.41</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -720,7 +720,7 @@
         <v>27138.5</v>
       </c>
       <c r="D10" s="5">
-        <v>2.48</v>
+        <v>24.8</v>
       </c>
     </row>
   </sheetData>
@@ -767,7 +767,7 @@
         <v>839.01269999999613</v>
       </c>
       <c r="E2">
-        <v>2.8</v>
+        <v>27.96</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -784,7 +784,7 @@
         <v>2502.7195999999612</v>
       </c>
       <c r="E3">
-        <v>2.78</v>
+        <v>27.76</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -801,7 +801,7 @@
         <v>12252.21879999991</v>
       </c>
       <c r="E4">
-        <v>1.4</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -818,7 +818,7 @@
         <v>46.171499999999995</v>
       </c>
       <c r="E5">
-        <v>3.27</v>
+        <v>32.700000000000003</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -835,7 +835,7 @@
         <v>497.87350000000112</v>
       </c>
       <c r="E6">
-        <v>2.5</v>
+        <v>25.01</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -852,7 +852,7 @@
         <v>2287.3942000000088</v>
       </c>
       <c r="E7">
-        <v>2.84</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -869,7 +869,7 @@
         <v>8494.5725000000675</v>
       </c>
       <c r="E8">
-        <v>0.87</v>
+        <v>8.7100000000000009</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -886,7 +886,7 @@
         <v>31.803399999999996</v>
       </c>
       <c r="E9">
-        <v>1.82</v>
+        <v>18.239999999999998</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -903,7 +903,7 @@
         <v>942.54880000000685</v>
       </c>
       <c r="E10">
-        <v>3.14</v>
+        <v>31.35</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -920,7 +920,7 @@
         <v>2789.6663000000212</v>
       </c>
       <c r="E11">
-        <v>3.36</v>
+        <v>33.630000000000003</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -937,7 +937,7 @@
         <v>10001.213500000045</v>
       </c>
       <c r="E12">
-        <v>1.01</v>
+        <v>10.119999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -954,7 +954,7 @@
         <v>99.242799999999946</v>
       </c>
       <c r="E13">
-        <v>2.93</v>
+        <v>29.32</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -971,7 +971,7 @@
         <v>1328.7443999999846</v>
       </c>
       <c r="E14">
-        <v>3.19</v>
+        <v>31.92</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -988,7 +988,7 @@
         <v>2864.9991999999529</v>
       </c>
       <c r="E15">
-        <v>2.96</v>
+        <v>29.56</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1005,7 +1005,7 @@
         <v>13191.750599999952</v>
       </c>
       <c r="E16">
-        <v>1.1599999999999999</v>
+        <v>11.57</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1022,7 +1022,7 @@
         <v>105.71420000000009</v>
       </c>
       <c r="E17">
-        <v>3.12</v>
+        <v>31.22</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1039,7 +1039,7 @@
         <v>1820.9819999999452</v>
       </c>
       <c r="E18">
-        <v>3.79</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1056,7 +1056,7 @@
         <v>3747.6184999999996</v>
       </c>
       <c r="E19">
-        <v>3.56</v>
+        <v>35.630000000000003</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1073,7 +1073,7 @@
         <v>19233.1641000001</v>
       </c>
       <c r="E20">
-        <v>1.98</v>
+        <v>19.75</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1090,7 +1090,7 @@
         <v>179.54179999999985</v>
       </c>
       <c r="E21">
-        <v>4.8</v>
+        <v>47.96</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1107,7 +1107,7 @@
         <v>1700.132899999973</v>
       </c>
       <c r="E22">
-        <v>3.25</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1124,7 +1124,7 @@
         <v>2556.6665999999959</v>
       </c>
       <c r="E23">
-        <v>2.4500000000000002</v>
+        <v>24.54</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1141,7 +1141,7 @@
         <v>17421.806999999873</v>
       </c>
       <c r="E24">
-        <v>1.79</v>
+        <v>17.87</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1158,7 +1158,7 @@
         <v>133.45860000000013</v>
       </c>
       <c r="E25">
-        <v>5.45</v>
+        <v>54.55</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1175,7 +1175,7 @@
         <v>2355.0319999999601</v>
       </c>
       <c r="E26">
-        <v>3.72</v>
+        <v>37.21</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1192,7 +1192,7 @@
         <v>3755.1778000000122</v>
       </c>
       <c r="E27">
-        <v>3.02</v>
+        <v>30.15</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1209,7 +1209,7 @@
         <v>18687.691999998908</v>
       </c>
       <c r="E28">
-        <v>1.84</v>
+        <v>18.39</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1226,7 +1226,7 @@
         <v>142.69010000000006</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>49.97</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1243,7 +1243,7 @@
         <v>2492.6301999999832</v>
       </c>
       <c r="E30">
-        <v>4.3600000000000003</v>
+        <v>43.64</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1260,7 +1260,7 @@
         <v>3565.822600000045</v>
       </c>
       <c r="E31">
-        <v>3.52</v>
+        <v>35.19</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1277,7 +1277,7 @@
         <v>18730.696000000728</v>
       </c>
       <c r="E32">
-        <v>1.91</v>
+        <v>19.07</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1294,7 +1294,7 @@
         <v>195.03699999999992</v>
       </c>
       <c r="E33">
-        <v>5.19</v>
+        <v>51.94</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1311,7 +1311,7 @@
         <v>2870.1008000000202</v>
       </c>
       <c r="E34">
-        <v>4.8600000000000003</v>
+        <v>48.61</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1328,7 +1328,7 @@
         <v>2940.7234000000299</v>
       </c>
       <c r="E35">
-        <v>3.01</v>
+        <v>30.06</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1345,7 +1345,7 @@
         <v>21132.860599998316</v>
       </c>
       <c r="E36">
-        <v>2.06</v>
+        <v>20.61</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1362,7 +1362,7 @@
         <v>194.84600000000017</v>
       </c>
       <c r="E37">
-        <v>4.5999999999999996</v>
+        <v>45.99</v>
       </c>
     </row>
   </sheetData>
